--- a/Ryan/Model Evaluation.xlsx
+++ b/Ryan/Model Evaluation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ryan\Documents\tugas_akhir\tugas_akhir\Ryan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F0DC3CD-DDC9-4967-A4A8-AB38A626BD47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F3E2A92-4868-4F37-A9D1-4C44FF97FA61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="3" xr2:uid="{25F6504E-FC9E-48A7-B958-C267B0DC07FC}"/>
   </bookViews>
@@ -509,8 +509,8 @@
       <xdr:rowOff>176213</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="5490862" cy="321498"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="5" name="TextBox 4">
@@ -552,6 +552,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -655,7 +656,7 @@
                           <a:rPr lang="en-ID" sz="1100" i="0">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
-                          <m:t>-10 </m:t>
+                          <m:t>−10 </m:t>
                         </m:r>
                         <m:r>
                           <m:rPr>
@@ -762,7 +763,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="5" name="TextBox 4">

--- a/Ryan/Model Evaluation.xlsx
+++ b/Ryan/Model Evaluation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ryan\Documents\tugas_akhir\tugas_akhir\Ryan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F3E2A92-4868-4F37-A9D1-4C44FF97FA61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B3F48D1-AB68-4C32-B994-CD2E55FE1BCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="3" xr2:uid="{25F6504E-FC9E-48A7-B958-C267B0DC07FC}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{25F6504E-FC9E-48A7-B958-C267B0DC07FC}"/>
   </bookViews>
   <sheets>
     <sheet name="Scenario" sheetId="1" r:id="rId1"/>
@@ -320,9 +320,6 @@
     <t>SP-5</t>
   </si>
   <si>
-    <t>Rumah desain minimalis modern bergaya scandinavian yang lokasinya strategis dekat stasiun KRL atau akses tol. Lingkungannya aman, jalan lebar untuk mobil, dan sirkulasi udara bagus.</t>
-  </si>
-  <si>
     <t>Hunian murah meriah yang dekat dengan pasar atau supermarket untuk kebutuhan sehari-hari. Akses mudah, lingkungan tenang dan damai, dan cocok untuk pekerja yang butuh tempat istirahat.</t>
   </si>
   <si>
@@ -363,6 +360,9 @@
   </si>
   <si>
     <t>Jumlah Atribut Dihindari (Sesudah)</t>
+  </si>
+  <si>
+    <t>Rumah desain minimalis modern, memiliki gaya scandinavian, lokasinya strategis dekat stasiun KRL atau akses tol. Lingkungannya aman, jalan lebar untuk mobil, dan sirkulasi udara bagus.</t>
   </si>
 </sst>
 </file>
@@ -1242,7 +1242,7 @@
         <v>26</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="57" x14ac:dyDescent="0.45">
@@ -1256,7 +1256,7 @@
         <v>27</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="57" x14ac:dyDescent="0.45">
@@ -1270,7 +1270,7 @@
         <v>28</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="57" x14ac:dyDescent="0.45">
@@ -1284,7 +1284,7 @@
         <v>29</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="57" x14ac:dyDescent="0.45">
@@ -1312,7 +1312,7 @@
         <v>31</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -2172,19 +2172,19 @@
         <v>34</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>62</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.45">
@@ -2192,7 +2192,7 @@
         <v>11</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C2" s="4">
         <v>8</v>
@@ -2214,7 +2214,7 @@
         <v>12</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C3" s="4">
         <v>2</v>
@@ -2236,7 +2236,7 @@
         <v>17</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C4" s="4">
         <v>5</v>
@@ -2258,7 +2258,7 @@
         <v>19</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C5" s="4">
         <v>3</v>
@@ -2280,7 +2280,7 @@
         <v>55</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C6" s="4">
         <v>2</v>
